--- a/data/certificates.xlsx
+++ b/data/certificates.xlsx
@@ -1,34 +1,123 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Makled\Desktop\portfolio, cv\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C1AECC-4E18-47EB-8207-787599DE3799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Issuer</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>ImagePath</t>
+  </si>
+  <si>
+    <t>AI Career Essentials Certificate</t>
+  </si>
+  <si>
+    <t>ALX</t>
+  </si>
+  <si>
+    <t>/assets/certificates/73-alx-aice-ai-career-essentials-certificate-ahmed-makled.png</t>
+  </si>
+  <si>
+    <t>ICPC ECPC Qualifications 2023 – 106th Place</t>
+  </si>
+  <si>
+    <t>ICPC Foundation</t>
+  </si>
+  <si>
+    <t>Successfully completed the 8-week AI Career Essentials program, covering AI fundamentals, workplace productivity, and professional development skills.</t>
+  </si>
+  <si>
+    <t>Participated in the 2023 ECPC Qualifications representing Damietta University and achieved 106th Place, demonstrating problem-solving and competitive programming skills.</t>
+  </si>
+  <si>
+    <t>2nd FCAI Tech Forum – Certificate of Appreciation</t>
+  </si>
+  <si>
+    <t>Faculty of Computers &amp; Artificial Intelligence, Damietta University</t>
+  </si>
+  <si>
+    <t>/assets/certificates/fcai-tech-forum.jpg</t>
+  </si>
+  <si>
+    <t>Summer Training Certificate – Computer Networks</t>
+  </si>
+  <si>
+    <t>/assets/certificates/summer-training.jpg</t>
+  </si>
+  <si>
+    <t>Awarded for active participation in the 2nd FCAI Tech Forum, recognizing engagement in technology and innovation events.</t>
+  </si>
+  <si>
+    <t>Successfully completed 54 hours of practical summer training in Computer Networks, covering networking fundamentals and hands-on laboratory activities.</t>
+  </si>
+  <si>
+    <t>/assets/certificates/2024-ECPCQDAYTWO2023-Ahmed Nasr Makled-PLACE.png</t>
+  </si>
+  <si>
+    <t>18/08/2024</t>
+  </si>
+  <si>
+    <t>08/08/2023</t>
+  </si>
+  <si>
+    <t>01/04/2025</t>
+  </si>
+  <si>
+    <t>14/08/2025</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="B1mmm\-yy"/>
+  </numFmts>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +135,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,121 +440,119 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.5703125" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="74" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Issuer</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ImagePath</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Flutter Development Certification</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Comprehensive Flutter development course covering widgets, state management, and app architecture.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>assets/images/profile.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cross-Platform Mobile Development</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NTI</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Advanced certification in cross-platform mobile app development with Flutter.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>assets/images/profile.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Firebase Integration</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Udemy</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Complete Firebase integration course for authentication, database, and cloud functions.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>assets/images/profile.jpg</t>
-        </is>
-      </c>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C11" s="1"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C12" s="1"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C13" s="1"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G14" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/certificates.xlsx
+++ b/data/certificates.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Makled\Desktop\portfolio, cv\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ahmed\05 Enhance Work\portfolio\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C1AECC-4E18-47EB-8207-787599DE3799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E8B2427-97CF-467E-B4DC-48C6FD0C2331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>Title</t>
   </si>
@@ -97,6 +97,18 @@
   </si>
   <si>
     <t>14/08/2025</t>
+  </si>
+  <si>
+    <t>/assets/certificates/Ahmed Nasr Makled NTI.jpg</t>
+  </si>
+  <si>
+    <t>Mobile App Development – Flutter</t>
+  </si>
+  <si>
+    <t>National Telecommunication Institute (NTI), Ministry of Communications and Information Technology (MCIT)</t>
+  </si>
+  <si>
+    <t>Completed 120 hours of Mobile App Development training, including 90 technical hours and 30 freelancing coaching hours, with a final score of 99%. Gained hands-on experience in Flutter, Firebase, REST APIs, Clean Architecture, state management, and professional software development practices.</t>
   </si>
 </sst>
 </file>
@@ -104,7 +116,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="B1mmm\-yy"/>
+    <numFmt numFmtId="164" formatCode="B1mmm\-yy"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -135,10 +147,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -444,10 +459,10 @@
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="1" max="1" width="46.5703125" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="44.85546875" customWidth="1"/>
     <col min="5" max="5" width="74" customWidth="1"/>
   </cols>
   <sheetData>
@@ -470,69 +485,86 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
+      </c>
+      <c r="C2" s="3">
+        <v>46071</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E6" t="s">
         <v>19</v>
       </c>
     </row>
